--- a/Design/Excel/GameHot/Datas/Buqi/BuqiTrainingProject.xlsx
+++ b/Design/Excel/GameHot/Datas/Buqi/BuqiTrainingProject.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuqiTrainingProject" sheetId="1" r:id="Rd0c5cf4323894c3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuqiTrainingProject" sheetId="1" r:id="Rb4971a5d65df4f4c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -396,7 +396,7 @@
         <x:v>trainer-wind</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>疾行诀</x:v>
+        <x:v>冷却训练 · 疾行</x:v>
       </x:c>
       <x:c r="E4" t="str">
         <x:v>Buqi.Content.Training.training_wind_01.Name</x:v>
@@ -413,7 +413,7 @@
       <x:c r="I4" t="str">
         <x:v>haste</x:v>
       </x:c>
-      <x:c r="J4" t="str"/>
+      <x:c r="J4"/>
       <x:c r="K4" t="str">
         <x:v>CooldownPercent</x:v>
       </x:c>
@@ -427,7 +427,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O4" t="str">
-        <x:v>本日所有加速标签器物基础冷却降低 10%。</x:v>
+        <x:v>本日所有加速标签装备基础冷却降低 10%。</x:v>
       </x:c>
       <x:c r="P4" t="str">
         <x:v>Buqi.Content.Training.training_wind_01.Summary</x:v>
@@ -442,7 +442,7 @@
         <x:v>trainer-wind</x:v>
       </x:c>
       <x:c r="D5" t="str">
-        <x:v>开脉风</x:v>
+        <x:v>攻击加速 · 开脉</x:v>
       </x:c>
       <x:c r="E5" t="str">
         <x:v>Buqi.Content.Training.training_wind_02.Name</x:v>
@@ -459,7 +459,7 @@
       <x:c r="I5" t="str">
         <x:v>attack</x:v>
       </x:c>
-      <x:c r="J5" t="str"/>
+      <x:c r="J5"/>
       <x:c r="K5" t="str">
         <x:v>OpeningHaste</x:v>
       </x:c>
@@ -473,7 +473,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O5" t="str">
-        <x:v>下一战开场使攻击器物加速 1000，持续 30 tick。</x:v>
+        <x:v>下一战开场使攻击装备加速 1000，持续 30 时间单位。</x:v>
       </x:c>
       <x:c r="P5" t="str">
         <x:v>Buqi.Content.Training.training_wind_02.Summary</x:v>
@@ -488,7 +488,7 @@
         <x:v>trainer-wind</x:v>
       </x:c>
       <x:c r="D6" t="str">
-        <x:v>邻响步</x:v>
+        <x:v>相邻加速 · 邻响</x:v>
       </x:c>
       <x:c r="E6" t="str">
         <x:v>Buqi.Content.Training.training_wind_03.Name</x:v>
@@ -505,7 +505,7 @@
       <x:c r="I6" t="str">
         <x:v>adjacent</x:v>
       </x:c>
-      <x:c r="J6" t="str"/>
+      <x:c r="J6"/>
       <x:c r="K6" t="str">
         <x:v>AdjacentHaste</x:v>
       </x:c>
@@ -519,7 +519,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O6" t="str">
-        <x:v>下一战首次邻接触发后，使相邻器物加速 800，持续 30 tick。</x:v>
+        <x:v>下一战首次邻接触发后，使相邻装备加速 800，持续 30 时间单位。</x:v>
       </x:c>
       <x:c r="P6" t="str">
         <x:v>Buqi.Content.Training.training_wind_03.Summary</x:v>
@@ -534,7 +534,7 @@
         <x:v>trainer-ward</x:v>
       </x:c>
       <x:c r="D7" t="str">
-        <x:v>垒息</x:v>
+        <x:v>开场护盾 · 垒息</x:v>
       </x:c>
       <x:c r="E7" t="str">
         <x:v>Buqi.Content.Training.training_ward_01.Name</x:v>
@@ -551,7 +551,7 @@
       <x:c r="I7" t="str">
         <x:v>shield</x:v>
       </x:c>
-      <x:c r="J7" t="str"/>
+      <x:c r="J7"/>
       <x:c r="K7" t="str">
         <x:v>OpeningBuffer</x:v>
       </x:c>
@@ -565,7 +565,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O7" t="str">
-        <x:v>下一战开场获得 6 点护体。</x:v>
+        <x:v>下一战开场获得 6 点护盾。</x:v>
       </x:c>
       <x:c r="P7" t="str">
         <x:v>Buqi.Content.Training.training_ward_01.Summary</x:v>
@@ -580,7 +580,7 @@
         <x:v>trainer-ward</x:v>
       </x:c>
       <x:c r="D8" t="str">
-        <x:v>守势</x:v>
+        <x:v>护盾强化 · 守势</x:v>
       </x:c>
       <x:c r="E8" t="str">
         <x:v>Buqi.Content.Training.training_ward_02.Name</x:v>
@@ -597,7 +597,7 @@
       <x:c r="I8" t="str">
         <x:v>shield</x:v>
       </x:c>
-      <x:c r="J8" t="str"/>
+      <x:c r="J8"/>
       <x:c r="K8" t="str">
         <x:v>BufferGainPercent</x:v>
       </x:c>
@@ -611,7 +611,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>本日护体获得量提高 15%。</x:v>
+        <x:v>本日护盾获得量提高 15%。</x:v>
       </x:c>
       <x:c r="P8" t="str">
         <x:v>Buqi.Content.Training.training_ward_02.Summary</x:v>
@@ -626,7 +626,7 @@
         <x:v>trainer-ward</x:v>
       </x:c>
       <x:c r="D9" t="str">
-        <x:v>定岳</x:v>
+        <x:v>受击护盾 · 定岳</x:v>
       </x:c>
       <x:c r="E9" t="str">
         <x:v>Buqi.Content.Training.training_ward_03.Name</x:v>
@@ -643,7 +643,7 @@
       <x:c r="I9" t="str">
         <x:v>counter</x:v>
       </x:c>
-      <x:c r="J9" t="str"/>
+      <x:c r="J9"/>
       <x:c r="K9" t="str">
         <x:v>FirstInterferenceWard</x:v>
       </x:c>
@@ -657,7 +657,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>下一战首次受到干扰时获得 8 点护体。</x:v>
+        <x:v>下一战首次受到干扰时获得 8 点护盾。</x:v>
       </x:c>
       <x:c r="P9" t="str">
         <x:v>Buqi.Content.Training.training_ward_03.Summary</x:v>
@@ -672,7 +672,7 @@
         <x:v>trainer-pulse</x:v>
       </x:c>
       <x:c r="D10" t="str">
-        <x:v>回气</x:v>
+        <x:v>开场恢复 · 回气</x:v>
       </x:c>
       <x:c r="E10" t="str">
         <x:v>Buqi.Content.Training.training_pulse_01.Name</x:v>
@@ -689,7 +689,7 @@
       <x:c r="I10" t="str">
         <x:v>heal</x:v>
       </x:c>
-      <x:c r="J10" t="str"/>
+      <x:c r="J10"/>
       <x:c r="K10" t="str">
         <x:v>OpeningHeal</x:v>
       </x:c>
@@ -718,7 +718,7 @@
         <x:v>trainer-pulse</x:v>
       </x:c>
       <x:c r="D11" t="str">
-        <x:v>续脉</x:v>
+        <x:v>治疗强化 · 续脉</x:v>
       </x:c>
       <x:c r="E11" t="str">
         <x:v>Buqi.Content.Training.training_pulse_02.Name</x:v>
@@ -735,7 +735,7 @@
       <x:c r="I11" t="str">
         <x:v>heal</x:v>
       </x:c>
-      <x:c r="J11" t="str"/>
+      <x:c r="J11"/>
       <x:c r="K11" t="str">
         <x:v>HealingPercent</x:v>
       </x:c>
@@ -764,7 +764,7 @@
         <x:v>trainer-pulse</x:v>
       </x:c>
       <x:c r="D12" t="str">
-        <x:v>长息</x:v>
+        <x:v>持续恢复 · 长息</x:v>
       </x:c>
       <x:c r="E12" t="str">
         <x:v>Buqi.Content.Training.training_pulse_03.Name</x:v>
@@ -781,7 +781,7 @@
       <x:c r="I12" t="str">
         <x:v>regen</x:v>
       </x:c>
-      <x:c r="J12" t="str"/>
+      <x:c r="J12"/>
       <x:c r="K12" t="str">
         <x:v>RegenDuration</x:v>
       </x:c>
@@ -795,7 +795,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>下一战生命恢复效果持续时间增加 20 tick。</x:v>
+        <x:v>下一战生命恢复效果持续时间增加 20 时间单位。</x:v>
       </x:c>
       <x:c r="P12" t="str">
         <x:v>Buqi.Content.Training.training_pulse_03.Summary</x:v>
@@ -810,7 +810,7 @@
         <x:v>trainer-craft</x:v>
       </x:c>
       <x:c r="D13" t="str">
-        <x:v>省材</x:v>
+        <x:v>升级折扣 · 省材</x:v>
       </x:c>
       <x:c r="E13" t="str">
         <x:v>Buqi.Content.Training.training_craft_01.Name</x:v>
@@ -827,7 +827,7 @@
       <x:c r="I13" t="str">
         <x:v>core</x:v>
       </x:c>
-      <x:c r="J13" t="str"/>
+      <x:c r="J13"/>
       <x:c r="K13" t="str">
         <x:v>UpgradeDiscount</x:v>
       </x:c>
@@ -841,7 +841,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>本日首次升级少花 1 灵石，最低仍为 1。</x:v>
+        <x:v>本日首次升级少花 1 金币，最低仍为 1。</x:v>
       </x:c>
       <x:c r="P13" t="str">
         <x:v>Buqi.Content.Training.training_craft_01.Summary</x:v>
@@ -856,7 +856,7 @@
         <x:v>trainer-craft</x:v>
       </x:c>
       <x:c r="D14" t="str">
-        <x:v>净炉</x:v>
+        <x:v>改造折扣 · 净炉</x:v>
       </x:c>
       <x:c r="E14" t="str">
         <x:v>Buqi.Content.Training.training_craft_02.Name</x:v>
@@ -873,7 +873,7 @@
       <x:c r="I14" t="str">
         <x:v>counter</x:v>
       </x:c>
-      <x:c r="J14" t="str"/>
+      <x:c r="J14"/>
       <x:c r="K14" t="str">
         <x:v>RefinementDiscount</x:v>
       </x:c>
@@ -887,7 +887,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>本日首次精炼少花 1 灵石，最低仍为 1。</x:v>
+        <x:v>本日首次改造少花 1 金币，最低仍为 1。</x:v>
       </x:c>
       <x:c r="P14" t="str">
         <x:v>Buqi.Content.Training.training_craft_02.Summary</x:v>
@@ -902,7 +902,7 @@
         <x:v>trainer-craft</x:v>
       </x:c>
       <x:c r="D15" t="str">
-        <x:v>识货</x:v>
+        <x:v>免费刷新 · 识货</x:v>
       </x:c>
       <x:c r="E15" t="str">
         <x:v>Buqi.Content.Training.training_craft_03.Name</x:v>
@@ -919,7 +919,7 @@
       <x:c r="I15" t="str">
         <x:v>economy</x:v>
       </x:c>
-      <x:c r="J15" t="str"/>
+      <x:c r="J15"/>
       <x:c r="K15" t="str">
         <x:v>ShopReroll</x:v>
       </x:c>
